--- a/output/topology_excel/763.xlsx
+++ b/output/topology_excel/763.xlsx
@@ -425,43 +425,58 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G13"/>
+  <dimension ref="A1:J13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>房间ID1</t>
+          <t>房间1</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>房间类型1</t>
+          <t>类型1</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>房间ID2</t>
+          <t>面积1</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>房间类型2</t>
+          <t>房间2</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
+          <t>类型2</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>面积2</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
           <t>连接类型</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>连接数量</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>连接面积</t>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>数量</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>length</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>width</t>
         </is>
       </c>
     </row>
@@ -475,202 +490,265 @@
         </is>
       </c>
       <c r="C2" t="n">
+        <v>457408</v>
+      </c>
+      <c r="D2" t="n">
         <v>5</v>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="E2" t="inlineStr">
         <is>
           <t>Bath</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>门/窗</t>
-        </is>
-      </c>
       <c r="F2" t="n">
-        <v>1</v>
-      </c>
-      <c r="G2" t="n">
-        <v>1080</v>
+        <v>78650</v>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>窗</t>
+        </is>
+      </c>
+      <c r="H2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I2" t="n">
+        <v>72</v>
+      </c>
+      <c r="J2" t="n">
+        <v>15</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Living Room</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>5</v>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>Bath</t>
-        </is>
+        <v>556806</v>
+      </c>
+      <c r="D3" t="n">
+        <v>2</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>墙</t>
+          <t>Bedroom</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>286</v>
-      </c>
-      <c r="G3" t="n">
-        <v>4290</v>
+        <v>134520</v>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>窗</t>
+        </is>
+      </c>
+      <c r="H3" t="n">
+        <v>1</v>
+      </c>
+      <c r="I3" t="n">
+        <v>81</v>
+      </c>
+      <c r="J3" t="n">
+        <v>12</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Living Room</t>
+          <t>Bath</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>2</v>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>Bedroom</t>
-        </is>
+        <v>78650</v>
+      </c>
+      <c r="D4" t="n">
+        <v>6</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>门/窗</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1</v>
-      </c>
-      <c r="G4" t="n">
-        <v>972</v>
+        <v>38756</v>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>窗</t>
+        </is>
+      </c>
+      <c r="H4" t="n">
+        <v>1</v>
+      </c>
+      <c r="I4" t="n">
+        <v>70</v>
+      </c>
+      <c r="J4" t="n">
+        <v>13</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Living Room</t>
+          <t>Bedroom</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>2</v>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>Bedroom</t>
-        </is>
+        <v>145329</v>
+      </c>
+      <c r="D5" t="n">
+        <v>4</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>墙</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>547</v>
-      </c>
-      <c r="G5" t="n">
-        <v>11666</v>
+        <v>457408</v>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>窗</t>
+        </is>
+      </c>
+      <c r="H5" t="n">
+        <v>1</v>
+      </c>
+      <c r="I5" t="n">
+        <v>68</v>
+      </c>
+      <c r="J5" t="n">
+        <v>66</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
+          <t>Living Room</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>556806</v>
+      </c>
+      <c r="D6" t="n">
+        <v>7</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
           <t>Bath</t>
         </is>
       </c>
-      <c r="C6" t="n">
-        <v>6</v>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>门/窗</t>
-        </is>
-      </c>
       <c r="F6" t="n">
-        <v>1</v>
-      </c>
-      <c r="G6" t="n">
-        <v>910</v>
+        <v>24153</v>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>窗</t>
+        </is>
+      </c>
+      <c r="H6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I6" t="n">
+        <v>77</v>
+      </c>
+      <c r="J6" t="n">
+        <v>42</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Bath</t>
+          <t>Living Room</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>6</v>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
+        <v>556806</v>
+      </c>
+      <c r="D7" t="n">
+        <v>2</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
+          <t>Bedroom</t>
+        </is>
+      </c>
+      <c r="F7" t="n">
+        <v>134520</v>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
           <t>墙</t>
         </is>
       </c>
-      <c r="F7" t="n">
-        <v>275</v>
-      </c>
-      <c r="G7" t="n">
-        <v>3575</v>
+      <c r="H7" t="n">
+        <v>1</v>
+      </c>
+      <c r="I7" t="n">
+        <v>500</v>
+      </c>
+      <c r="J7" t="n">
+        <v>179</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Living Room</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>4</v>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
+        <v>556806</v>
+      </c>
+      <c r="D8" t="n">
+        <v>7</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>门/窗</t>
+          <t>Bath</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1</v>
-      </c>
-      <c r="G8" t="n">
-        <v>1125</v>
+        <v>24153</v>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>墙</t>
+        </is>
+      </c>
+      <c r="H8" t="n">
+        <v>1</v>
+      </c>
+      <c r="I8" t="n">
+        <v>366</v>
+      </c>
+      <c r="J8" t="n">
+        <v>150</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
@@ -678,139 +756,184 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>4</v>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
+        <v>134520</v>
+      </c>
+      <c r="D9" t="n">
+        <v>7</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
+          <t>Bath</t>
+        </is>
+      </c>
+      <c r="F9" t="n">
+        <v>24153</v>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
           <t>墙</t>
         </is>
       </c>
-      <c r="F9" t="n">
-        <v>726</v>
-      </c>
-      <c r="G9" t="n">
-        <v>12077</v>
+      <c r="H9" t="n">
+        <v>1</v>
+      </c>
+      <c r="I9" t="n">
+        <v>187</v>
+      </c>
+      <c r="J9" t="n">
+        <v>10</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Living Room</t>
+          <t>Bedroom</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>7</v>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>Bath</t>
-        </is>
+        <v>145329</v>
+      </c>
+      <c r="D10" t="n">
+        <v>4</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>门/窗</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>1</v>
-      </c>
-      <c r="G10" t="n">
-        <v>817</v>
+        <v>457408</v>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>墙</t>
+        </is>
+      </c>
+      <c r="H10" t="n">
+        <v>1</v>
+      </c>
+      <c r="I10" t="n">
+        <v>447</v>
+      </c>
+      <c r="J10" t="n">
+        <v>359</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Living Room</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>7</v>
-      </c>
-      <c r="D11" t="inlineStr">
+        <v>457408</v>
+      </c>
+      <c r="D11" t="n">
+        <v>5</v>
+      </c>
+      <c r="E11" t="inlineStr">
         <is>
           <t>Bath</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
+      <c r="F11" t="n">
+        <v>78650</v>
+      </c>
+      <c r="G11" t="inlineStr">
         <is>
           <t>墙</t>
         </is>
       </c>
-      <c r="F11" t="n">
-        <v>260</v>
-      </c>
-      <c r="G11" t="n">
-        <v>7062</v>
+      <c r="H11" t="n">
+        <v>1</v>
+      </c>
+      <c r="I11" t="n">
+        <v>286</v>
+      </c>
+      <c r="J11" t="n">
+        <v>15</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>7</v>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>Bath</t>
-        </is>
+        <v>457408</v>
+      </c>
+      <c r="D12" t="n">
+        <v>6</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="F12" t="n">
+        <v>38756</v>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
           <t>墙</t>
         </is>
       </c>
-      <c r="F12" t="n">
-        <v>187</v>
-      </c>
-      <c r="G12" t="n">
-        <v>1870</v>
+      <c r="H12" t="n">
+        <v>1</v>
+      </c>
+      <c r="I12" t="n">
+        <v>354</v>
+      </c>
+      <c r="J12" t="n">
+        <v>200</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
+          <t>Bath</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>78650</v>
+      </c>
+      <c r="D13" t="n">
+        <v>6</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
           <t>Other</t>
         </is>
       </c>
-      <c r="C13" t="n">
-        <v>6</v>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
+      <c r="F13" t="n">
+        <v>38756</v>
+      </c>
+      <c r="G13" t="inlineStr">
         <is>
           <t>墙</t>
         </is>
       </c>
-      <c r="F13" t="n">
-        <v>373</v>
-      </c>
-      <c r="G13" t="n">
-        <v>14739</v>
+      <c r="H13" t="n">
+        <v>1</v>
+      </c>
+      <c r="I13" t="n">
+        <v>275</v>
+      </c>
+      <c r="J13" t="n">
+        <v>13</v>
       </c>
     </row>
   </sheetData>

--- a/output/topology_excel/763.xlsx
+++ b/output/topology_excel/763.xlsx
@@ -505,7 +505,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>窗</t>
+          <t>门</t>
         </is>
       </c>
       <c r="H2" t="n">
@@ -543,7 +543,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>窗</t>
+          <t>门</t>
         </is>
       </c>
       <c r="H3" t="n">
@@ -581,7 +581,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>窗</t>
+          <t>门</t>
         </is>
       </c>
       <c r="H4" t="n">
@@ -619,7 +619,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>窗</t>
+          <t>门</t>
         </is>
       </c>
       <c r="H5" t="n">
@@ -657,7 +657,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>窗</t>
+          <t>门</t>
         </is>
       </c>
       <c r="H6" t="n">
@@ -740,10 +740,10 @@
         <v>1</v>
       </c>
       <c r="I8" t="n">
-        <v>366</v>
+        <v>237</v>
       </c>
       <c r="J8" t="n">
-        <v>150</v>
+        <v>149</v>
       </c>
     </row>
     <row r="9">
@@ -892,7 +892,7 @@
         <v>1</v>
       </c>
       <c r="I12" t="n">
-        <v>354</v>
+        <v>290</v>
       </c>
       <c r="J12" t="n">
         <v>200</v>

--- a/output/topology_excel/763.xlsx
+++ b/output/topology_excel/763.xlsx
@@ -425,58 +425,38 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J13"/>
+  <dimension ref="A1:F13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>房间1</t>
+          <t>RoomA</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>类型1</t>
+          <t>RoomB</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>面积1</t>
+          <t>ConnectionType</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>房间2</t>
+          <t>Count</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>类型2</t>
+          <t>Length</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>面积2</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>连接类型</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>数量</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>length</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>width</t>
+          <t>Width</t>
         </is>
       </c>
     </row>
@@ -484,37 +464,21 @@
       <c r="A2" t="n">
         <v>4</v>
       </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
-      </c>
-      <c r="C2" t="n">
-        <v>457408</v>
+      <c r="B2" t="n">
+        <v>5</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Door</t>
+        </is>
       </c>
       <c r="D2" t="n">
-        <v>5</v>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>Bath</t>
-        </is>
+        <v>1</v>
+      </c>
+      <c r="E2" t="n">
+        <v>72</v>
       </c>
       <c r="F2" t="n">
-        <v>78650</v>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>门</t>
-        </is>
-      </c>
-      <c r="H2" t="n">
-        <v>1</v>
-      </c>
-      <c r="I2" t="n">
-        <v>72</v>
-      </c>
-      <c r="J2" t="n">
         <v>15</v>
       </c>
     </row>
@@ -522,37 +486,21 @@
       <c r="A3" t="n">
         <v>1</v>
       </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>Living Room</t>
-        </is>
-      </c>
-      <c r="C3" t="n">
-        <v>556806</v>
+      <c r="B3" t="n">
+        <v>2</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Door</t>
+        </is>
       </c>
       <c r="D3" t="n">
-        <v>2</v>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>Bedroom</t>
-        </is>
+        <v>1</v>
+      </c>
+      <c r="E3" t="n">
+        <v>81</v>
       </c>
       <c r="F3" t="n">
-        <v>134520</v>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>门</t>
-        </is>
-      </c>
-      <c r="H3" t="n">
-        <v>1</v>
-      </c>
-      <c r="I3" t="n">
-        <v>81</v>
-      </c>
-      <c r="J3" t="n">
         <v>12</v>
       </c>
     </row>
@@ -560,37 +508,21 @@
       <c r="A4" t="n">
         <v>5</v>
       </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Bath</t>
-        </is>
-      </c>
-      <c r="C4" t="n">
-        <v>78650</v>
+      <c r="B4" t="n">
+        <v>6</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Door</t>
+        </is>
       </c>
       <c r="D4" t="n">
-        <v>6</v>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
+        <v>1</v>
+      </c>
+      <c r="E4" t="n">
+        <v>70</v>
       </c>
       <c r="F4" t="n">
-        <v>38756</v>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>门</t>
-        </is>
-      </c>
-      <c r="H4" t="n">
-        <v>1</v>
-      </c>
-      <c r="I4" t="n">
-        <v>70</v>
-      </c>
-      <c r="J4" t="n">
         <v>13</v>
       </c>
     </row>
@@ -598,37 +530,21 @@
       <c r="A5" t="n">
         <v>3</v>
       </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Bedroom</t>
-        </is>
-      </c>
-      <c r="C5" t="n">
-        <v>145329</v>
+      <c r="B5" t="n">
+        <v>4</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Door</t>
+        </is>
       </c>
       <c r="D5" t="n">
-        <v>4</v>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
+        <v>1</v>
+      </c>
+      <c r="E5" t="n">
+        <v>68</v>
       </c>
       <c r="F5" t="n">
-        <v>457408</v>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>门</t>
-        </is>
-      </c>
-      <c r="H5" t="n">
-        <v>1</v>
-      </c>
-      <c r="I5" t="n">
-        <v>68</v>
-      </c>
-      <c r="J5" t="n">
         <v>66</v>
       </c>
     </row>
@@ -636,37 +552,21 @@
       <c r="A6" t="n">
         <v>1</v>
       </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Living Room</t>
-        </is>
-      </c>
-      <c r="C6" t="n">
-        <v>556806</v>
+      <c r="B6" t="n">
+        <v>7</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Door</t>
+        </is>
       </c>
       <c r="D6" t="n">
-        <v>7</v>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>Bath</t>
-        </is>
+        <v>1</v>
+      </c>
+      <c r="E6" t="n">
+        <v>77</v>
       </c>
       <c r="F6" t="n">
-        <v>24153</v>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>门</t>
-        </is>
-      </c>
-      <c r="H6" t="n">
-        <v>1</v>
-      </c>
-      <c r="I6" t="n">
-        <v>77</v>
-      </c>
-      <c r="J6" t="n">
         <v>42</v>
       </c>
     </row>
@@ -674,37 +574,21 @@
       <c r="A7" t="n">
         <v>1</v>
       </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>Living Room</t>
-        </is>
-      </c>
-      <c r="C7" t="n">
-        <v>556806</v>
+      <c r="B7" t="n">
+        <v>2</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Wall</t>
+        </is>
       </c>
       <c r="D7" t="n">
-        <v>2</v>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>Bedroom</t>
-        </is>
+        <v>1</v>
+      </c>
+      <c r="E7" t="n">
+        <v>500</v>
       </c>
       <c r="F7" t="n">
-        <v>134520</v>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>墙</t>
-        </is>
-      </c>
-      <c r="H7" t="n">
-        <v>1</v>
-      </c>
-      <c r="I7" t="n">
-        <v>500</v>
-      </c>
-      <c r="J7" t="n">
         <v>179</v>
       </c>
     </row>
@@ -712,37 +596,21 @@
       <c r="A8" t="n">
         <v>1</v>
       </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>Living Room</t>
-        </is>
-      </c>
-      <c r="C8" t="n">
-        <v>556806</v>
+      <c r="B8" t="n">
+        <v>7</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Wall</t>
+        </is>
       </c>
       <c r="D8" t="n">
-        <v>7</v>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>Bath</t>
-        </is>
+        <v>1</v>
+      </c>
+      <c r="E8" t="n">
+        <v>237</v>
       </c>
       <c r="F8" t="n">
-        <v>24153</v>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>墙</t>
-        </is>
-      </c>
-      <c r="H8" t="n">
-        <v>1</v>
-      </c>
-      <c r="I8" t="n">
-        <v>237</v>
-      </c>
-      <c r="J8" t="n">
         <v>149</v>
       </c>
     </row>
@@ -750,37 +618,21 @@
       <c r="A9" t="n">
         <v>2</v>
       </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>Bedroom</t>
-        </is>
-      </c>
-      <c r="C9" t="n">
-        <v>134520</v>
+      <c r="B9" t="n">
+        <v>7</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Wall</t>
+        </is>
       </c>
       <c r="D9" t="n">
-        <v>7</v>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>Bath</t>
-        </is>
+        <v>1</v>
+      </c>
+      <c r="E9" t="n">
+        <v>187</v>
       </c>
       <c r="F9" t="n">
-        <v>24153</v>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>墙</t>
-        </is>
-      </c>
-      <c r="H9" t="n">
-        <v>1</v>
-      </c>
-      <c r="I9" t="n">
-        <v>187</v>
-      </c>
-      <c r="J9" t="n">
         <v>10</v>
       </c>
     </row>
@@ -788,37 +640,21 @@
       <c r="A10" t="n">
         <v>3</v>
       </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>Bedroom</t>
-        </is>
-      </c>
-      <c r="C10" t="n">
-        <v>145329</v>
+      <c r="B10" t="n">
+        <v>4</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Wall</t>
+        </is>
       </c>
       <c r="D10" t="n">
-        <v>4</v>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
+        <v>1</v>
+      </c>
+      <c r="E10" t="n">
+        <v>447</v>
       </c>
       <c r="F10" t="n">
-        <v>457408</v>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>墙</t>
-        </is>
-      </c>
-      <c r="H10" t="n">
-        <v>1</v>
-      </c>
-      <c r="I10" t="n">
-        <v>447</v>
-      </c>
-      <c r="J10" t="n">
         <v>359</v>
       </c>
     </row>
@@ -826,37 +662,21 @@
       <c r="A11" t="n">
         <v>4</v>
       </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
-      </c>
-      <c r="C11" t="n">
-        <v>457408</v>
+      <c r="B11" t="n">
+        <v>5</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Wall</t>
+        </is>
       </c>
       <c r="D11" t="n">
-        <v>5</v>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>Bath</t>
-        </is>
+        <v>1</v>
+      </c>
+      <c r="E11" t="n">
+        <v>286</v>
       </c>
       <c r="F11" t="n">
-        <v>78650</v>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>墙</t>
-        </is>
-      </c>
-      <c r="H11" t="n">
-        <v>1</v>
-      </c>
-      <c r="I11" t="n">
-        <v>286</v>
-      </c>
-      <c r="J11" t="n">
         <v>15</v>
       </c>
     </row>
@@ -864,37 +684,21 @@
       <c r="A12" t="n">
         <v>4</v>
       </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
-      </c>
-      <c r="C12" t="n">
-        <v>457408</v>
+      <c r="B12" t="n">
+        <v>6</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Wall</t>
+        </is>
       </c>
       <c r="D12" t="n">
-        <v>6</v>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
+        <v>1</v>
+      </c>
+      <c r="E12" t="n">
+        <v>290</v>
       </c>
       <c r="F12" t="n">
-        <v>38756</v>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>墙</t>
-        </is>
-      </c>
-      <c r="H12" t="n">
-        <v>1</v>
-      </c>
-      <c r="I12" t="n">
-        <v>290</v>
-      </c>
-      <c r="J12" t="n">
         <v>200</v>
       </c>
     </row>
@@ -902,37 +706,21 @@
       <c r="A13" t="n">
         <v>5</v>
       </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>Bath</t>
-        </is>
-      </c>
-      <c r="C13" t="n">
-        <v>78650</v>
+      <c r="B13" t="n">
+        <v>6</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Wall</t>
+        </is>
       </c>
       <c r="D13" t="n">
-        <v>6</v>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
+        <v>1</v>
+      </c>
+      <c r="E13" t="n">
+        <v>275</v>
       </c>
       <c r="F13" t="n">
-        <v>38756</v>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>墙</t>
-        </is>
-      </c>
-      <c r="H13" t="n">
-        <v>1</v>
-      </c>
-      <c r="I13" t="n">
-        <v>275</v>
-      </c>
-      <c r="J13" t="n">
         <v>13</v>
       </c>
     </row>

--- a/output/topology_excel/763.xlsx
+++ b/output/topology_excel/763.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F13"/>
+  <dimension ref="A1:F17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -462,10 +462,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B2" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -487,7 +487,7 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -509,7 +509,7 @@
         <v>5</v>
       </c>
       <c r="B4" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -528,10 +528,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B5" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -550,7 +550,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="B6" t="n">
         <v>7</v>
@@ -575,7 +575,7 @@
         <v>1</v>
       </c>
       <c r="B7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -586,15 +586,15 @@
         <v>1</v>
       </c>
       <c r="E7" t="n">
-        <v>500</v>
+        <v>380</v>
       </c>
       <c r="F7" t="n">
-        <v>179</v>
+        <v>12</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B8" t="n">
         <v>7</v>
@@ -608,15 +608,15 @@
         <v>1</v>
       </c>
       <c r="E8" t="n">
-        <v>237</v>
+        <v>249</v>
       </c>
       <c r="F8" t="n">
-        <v>149</v>
+        <v>22</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B9" t="n">
         <v>7</v>
@@ -630,10 +630,10 @@
         <v>1</v>
       </c>
       <c r="E9" t="n">
-        <v>187</v>
+        <v>167</v>
       </c>
       <c r="F9" t="n">
-        <v>10</v>
+        <v>120</v>
       </c>
     </row>
     <row r="10">
@@ -641,7 +641,7 @@
         <v>3</v>
       </c>
       <c r="B10" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -652,10 +652,10 @@
         <v>1</v>
       </c>
       <c r="E10" t="n">
-        <v>447</v>
+        <v>187</v>
       </c>
       <c r="F10" t="n">
-        <v>359</v>
+        <v>10</v>
       </c>
     </row>
     <row r="11">
@@ -663,7 +663,7 @@
         <v>4</v>
       </c>
       <c r="B11" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -674,18 +674,18 @@
         <v>1</v>
       </c>
       <c r="E11" t="n">
-        <v>286</v>
+        <v>447</v>
       </c>
       <c r="F11" t="n">
-        <v>15</v>
+        <v>359</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B12" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -696,10 +696,10 @@
         <v>1</v>
       </c>
       <c r="E12" t="n">
-        <v>290</v>
+        <v>286</v>
       </c>
       <c r="F12" t="n">
-        <v>200</v>
+        <v>15</v>
       </c>
     </row>
     <row r="13">
@@ -707,7 +707,7 @@
         <v>5</v>
       </c>
       <c r="B13" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -722,6 +722,94 @@
       </c>
       <c r="F13" t="n">
         <v>13</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>6</v>
+      </c>
+      <c r="B14" t="n">
+        <v>7</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Wall</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>1</v>
+      </c>
+      <c r="E14" t="n">
+        <v>237</v>
+      </c>
+      <c r="F14" t="n">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>8</v>
+      </c>
+      <c r="B15" t="n">
+        <v>9</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Wall</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>1</v>
+      </c>
+      <c r="E15" t="n">
+        <v>290</v>
+      </c>
+      <c r="F15" t="n">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>1</v>
+      </c>
+      <c r="B16" t="n">
+        <v>2</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Opening</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>1</v>
+      </c>
+      <c r="E16" t="n">
+        <v>487</v>
+      </c>
+      <c r="F16" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>2</v>
+      </c>
+      <c r="B17" t="n">
+        <v>7</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Opening</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>1</v>
+      </c>
+      <c r="E17" t="n">
+        <v>217</v>
+      </c>
+      <c r="F17" t="n">
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/output/topology_excel/763.xlsx
+++ b/output/topology_excel/763.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F17"/>
+  <dimension ref="A1:T17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -451,12 +451,82 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>Length</t>
+          <t>Length_1</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>Width</t>
+          <t>Width_1</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Length_2</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Width_2</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Length_3</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Width_3</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Length_4</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>Width_4</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>Length_5</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>Width_5</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>Length_6</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>Width_6</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>Length_7</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>Width_7</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>Length_8</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>Width_8</t>
         </is>
       </c>
     </row>
@@ -481,6 +551,20 @@
       <c r="F2" t="n">
         <v>15</v>
       </c>
+      <c r="G2" t="inlineStr"/>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
+      <c r="O2" t="inlineStr"/>
+      <c r="P2" t="inlineStr"/>
+      <c r="Q2" t="inlineStr"/>
+      <c r="R2" t="inlineStr"/>
+      <c r="S2" t="inlineStr"/>
+      <c r="T2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -503,6 +587,20 @@
       <c r="F3" t="n">
         <v>12</v>
       </c>
+      <c r="G3" t="inlineStr"/>
+      <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
+      <c r="O3" t="inlineStr"/>
+      <c r="P3" t="inlineStr"/>
+      <c r="Q3" t="inlineStr"/>
+      <c r="R3" t="inlineStr"/>
+      <c r="S3" t="inlineStr"/>
+      <c r="T3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -525,6 +623,20 @@
       <c r="F4" t="n">
         <v>13</v>
       </c>
+      <c r="G4" t="inlineStr"/>
+      <c r="H4" t="inlineStr"/>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
+      <c r="O4" t="inlineStr"/>
+      <c r="P4" t="inlineStr"/>
+      <c r="Q4" t="inlineStr"/>
+      <c r="R4" t="inlineStr"/>
+      <c r="S4" t="inlineStr"/>
+      <c r="T4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -547,6 +659,20 @@
       <c r="F5" t="n">
         <v>66</v>
       </c>
+      <c r="G5" t="inlineStr"/>
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="O5" t="inlineStr"/>
+      <c r="P5" t="inlineStr"/>
+      <c r="Q5" t="inlineStr"/>
+      <c r="R5" t="inlineStr"/>
+      <c r="S5" t="inlineStr"/>
+      <c r="T5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -569,6 +695,20 @@
       <c r="F6" t="n">
         <v>42</v>
       </c>
+      <c r="G6" t="inlineStr"/>
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+      <c r="O6" t="inlineStr"/>
+      <c r="P6" t="inlineStr"/>
+      <c r="Q6" t="inlineStr"/>
+      <c r="R6" t="inlineStr"/>
+      <c r="S6" t="inlineStr"/>
+      <c r="T6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -591,6 +731,20 @@
       <c r="F7" t="n">
         <v>12</v>
       </c>
+      <c r="G7" t="inlineStr"/>
+      <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
+      <c r="O7" t="inlineStr"/>
+      <c r="P7" t="inlineStr"/>
+      <c r="Q7" t="inlineStr"/>
+      <c r="R7" t="inlineStr"/>
+      <c r="S7" t="inlineStr"/>
+      <c r="T7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -611,8 +765,22 @@
         <v>249</v>
       </c>
       <c r="F8" t="n">
-        <v>22</v>
-      </c>
+        <v>14</v>
+      </c>
+      <c r="G8" t="inlineStr"/>
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
+      <c r="O8" t="inlineStr"/>
+      <c r="P8" t="inlineStr"/>
+      <c r="Q8" t="inlineStr"/>
+      <c r="R8" t="inlineStr"/>
+      <c r="S8" t="inlineStr"/>
+      <c r="T8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -633,8 +801,22 @@
         <v>167</v>
       </c>
       <c r="F9" t="n">
-        <v>120</v>
-      </c>
+        <v>43</v>
+      </c>
+      <c r="G9" t="inlineStr"/>
+      <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
+      <c r="O9" t="inlineStr"/>
+      <c r="P9" t="inlineStr"/>
+      <c r="Q9" t="inlineStr"/>
+      <c r="R9" t="inlineStr"/>
+      <c r="S9" t="inlineStr"/>
+      <c r="T9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -657,6 +839,20 @@
       <c r="F10" t="n">
         <v>10</v>
       </c>
+      <c r="G10" t="inlineStr"/>
+      <c r="H10" t="inlineStr"/>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
+      <c r="O10" t="inlineStr"/>
+      <c r="P10" t="inlineStr"/>
+      <c r="Q10" t="inlineStr"/>
+      <c r="R10" t="inlineStr"/>
+      <c r="S10" t="inlineStr"/>
+      <c r="T10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -677,8 +873,22 @@
         <v>447</v>
       </c>
       <c r="F11" t="n">
-        <v>359</v>
-      </c>
+        <v>27</v>
+      </c>
+      <c r="G11" t="inlineStr"/>
+      <c r="H11" t="inlineStr"/>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
+      <c r="O11" t="inlineStr"/>
+      <c r="P11" t="inlineStr"/>
+      <c r="Q11" t="inlineStr"/>
+      <c r="R11" t="inlineStr"/>
+      <c r="S11" t="inlineStr"/>
+      <c r="T11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -701,6 +911,20 @@
       <c r="F12" t="n">
         <v>15</v>
       </c>
+      <c r="G12" t="inlineStr"/>
+      <c r="H12" t="inlineStr"/>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
+      <c r="O12" t="inlineStr"/>
+      <c r="P12" t="inlineStr"/>
+      <c r="Q12" t="inlineStr"/>
+      <c r="R12" t="inlineStr"/>
+      <c r="S12" t="inlineStr"/>
+      <c r="T12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -723,6 +947,20 @@
       <c r="F13" t="n">
         <v>13</v>
       </c>
+      <c r="G13" t="inlineStr"/>
+      <c r="H13" t="inlineStr"/>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
+      <c r="O13" t="inlineStr"/>
+      <c r="P13" t="inlineStr"/>
+      <c r="Q13" t="inlineStr"/>
+      <c r="R13" t="inlineStr"/>
+      <c r="S13" t="inlineStr"/>
+      <c r="T13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -737,13 +975,55 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="E14" t="n">
-        <v>237</v>
+        <v>98</v>
       </c>
       <c r="F14" t="n">
-        <v>149</v>
+        <v>50</v>
+      </c>
+      <c r="G14" t="n">
+        <v>11</v>
+      </c>
+      <c r="H14" t="n">
+        <v>1</v>
+      </c>
+      <c r="I14" t="n">
+        <v>11</v>
+      </c>
+      <c r="J14" t="n">
+        <v>1</v>
+      </c>
+      <c r="K14" t="n">
+        <v>11</v>
+      </c>
+      <c r="L14" t="n">
+        <v>1</v>
+      </c>
+      <c r="M14" t="n">
+        <v>11</v>
+      </c>
+      <c r="N14" t="n">
+        <v>1</v>
+      </c>
+      <c r="O14" t="n">
+        <v>11</v>
+      </c>
+      <c r="P14" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>11</v>
+      </c>
+      <c r="R14" t="n">
+        <v>1</v>
+      </c>
+      <c r="S14" t="n">
+        <v>173</v>
+      </c>
+      <c r="T14" t="n">
+        <v>10</v>
       </c>
     </row>
     <row r="15">
@@ -759,14 +1039,36 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E15" t="n">
-        <v>290</v>
+        <v>64</v>
       </c>
       <c r="F15" t="n">
-        <v>200</v>
-      </c>
+        <v>15</v>
+      </c>
+      <c r="G15" t="n">
+        <v>123</v>
+      </c>
+      <c r="H15" t="n">
+        <v>68</v>
+      </c>
+      <c r="I15" t="n">
+        <v>172</v>
+      </c>
+      <c r="J15" t="n">
+        <v>13</v>
+      </c>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
+      <c r="O15" t="inlineStr"/>
+      <c r="P15" t="inlineStr"/>
+      <c r="Q15" t="inlineStr"/>
+      <c r="R15" t="inlineStr"/>
+      <c r="S15" t="inlineStr"/>
+      <c r="T15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -789,6 +1091,20 @@
       <c r="F16" t="n">
         <v>1</v>
       </c>
+      <c r="G16" t="inlineStr"/>
+      <c r="H16" t="inlineStr"/>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
+      <c r="O16" t="inlineStr"/>
+      <c r="P16" t="inlineStr"/>
+      <c r="Q16" t="inlineStr"/>
+      <c r="R16" t="inlineStr"/>
+      <c r="S16" t="inlineStr"/>
+      <c r="T16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -811,6 +1127,20 @@
       <c r="F17" t="n">
         <v>1</v>
       </c>
+      <c r="G17" t="inlineStr"/>
+      <c r="H17" t="inlineStr"/>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
+      <c r="O17" t="inlineStr"/>
+      <c r="P17" t="inlineStr"/>
+      <c r="Q17" t="inlineStr"/>
+      <c r="R17" t="inlineStr"/>
+      <c r="S17" t="inlineStr"/>
+      <c r="T17" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
